--- a/doc/仕様書.xlsx
+++ b/doc/仕様書.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirit_ygjlq3s\Desktop\Development\Project\MyEngine\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8335F8A7-8E17-4DA8-8EDD-13CBA37F9F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD0B7A6-8CC4-4A19-8ECF-043850642B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{007E28DE-F532-4133-89C6-A8AB1947F25D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{007E28DE-F532-4133-89C6-A8AB1947F25D}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
     <sheet name="ゲーム概要" sheetId="2" r:id="rId2"/>
     <sheet name="ゲームフロー" sheetId="3" r:id="rId3"/>
+    <sheet name="タイトル" sheetId="6" r:id="rId4"/>
+    <sheet name="メニュー" sheetId="7" r:id="rId5"/>
+    <sheet name="プレイヤー" sheetId="4" r:id="rId6"/>
+    <sheet name="敵" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -120,6 +124,200 @@
   </si>
   <si>
     <t>effect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特になし</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パラメーター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム画面</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択したキャラID</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化状態のConfigファイル</t>
+    <rPh sb="0" eb="4">
+      <t>キョウカジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要なパラメーター</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在のレベル</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在の経験値</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ケイケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本ステータス：CSVから読み込み</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム中のステータス</t>
+    <rPh sb="3" eb="4">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベル関係：次のレベルの必要経験値 = 基準値 × (レベル ^ 係数)</t>
+    <rPh sb="3" eb="5">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ倍率</t>
+    <rPh sb="4" eb="6">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クールタイム短縮率</t>
+    <rPh sb="6" eb="8">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期魔法の識別ID</t>
+    <rPh sb="0" eb="4">
+      <t>ショキマホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シキベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のレベルまでに必要な経験値</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ケイケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在の体力</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大体力</t>
+    <rPh sb="0" eb="4">
+      <t>サイダイタイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クールタイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面イメージ</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -144,7 +342,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +352,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -172,11 +382,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -194,6 +416,1753 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>248384</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>110636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457934</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>30772</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形: 角を丸くする 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F51228E6-2DF8-70EB-9788-45CDBF607B0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="248384" y="1777511"/>
+          <a:ext cx="895350" cy="396386"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>タイトル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>58617</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>118695</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>265236</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38831</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形: 角を丸くする 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F750C42-8CB8-482B-962C-1E7874DFA79C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2116017" y="1785570"/>
+          <a:ext cx="892419" cy="396386"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メニュー</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457934</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>70704</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>58617</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>78763</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E04770E6-B122-EC2E-9A7B-393E7E962F17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1143734" y="1975704"/>
+          <a:ext cx="972283" cy="8059"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>658692</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>128220</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>179511</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>48356</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32EC489A-DDE3-4493-8F3E-2C257896013D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4773492" y="1795095"/>
+          <a:ext cx="892419" cy="396386"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ゲーム</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>265236</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>78763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>658692</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="直線矢印コネクタ 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0730A05-1F58-456B-AE80-1EAD373E5C03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="8" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3008436" y="1983763"/>
+          <a:ext cx="1765056" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>677742</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>13920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="四角形: 角を丸くする 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B082EBE4-CB03-45C4-A046-6E039F5E86BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3420942" y="2871420"/>
+          <a:ext cx="1027233" cy="376605"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>キャラ選択</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>30042</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>175845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>236661</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95981</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="四角形: 角を丸くする 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4581FFF1-95FF-43D9-83F1-473DB0577D7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3459042" y="3509595"/>
+          <a:ext cx="892419" cy="396386"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>強化</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>58617</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>71070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>265236</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>229331</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="四角形: 角を丸くする 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F9A76D6-6476-4F00-ABC2-6E7115711F01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3487617" y="4119195"/>
+          <a:ext cx="892419" cy="396386"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>設定</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>504827</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>677742</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>202222</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="コネクタ: カギ線 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2177F1D5-DF55-35A1-1626-FD063887F2B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="27" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2552701" y="2191481"/>
+          <a:ext cx="877767" cy="858715"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>504826</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38831</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>30041</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>135913</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="コネクタ: カギ線 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B4D24B0-8B62-4406-B63E-3F5EAFD3B9FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="28" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2247718" y="2496464"/>
+          <a:ext cx="1525832" cy="896815"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>504827</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38831</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>58617</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>31138</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="コネクタ: カギ線 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{073E0A7C-208E-42E8-92A2-E695195529A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="29" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="1957206" y="2786977"/>
+          <a:ext cx="2135432" cy="925390"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>179511</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>35535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>115768</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88288</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="直線矢印コネクタ 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0287A6C3-08DC-4F82-B565-0AFB08E8C0CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="52" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5665911" y="1702410"/>
+          <a:ext cx="3365257" cy="290878"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>419102</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>48355</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>439617</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>87922</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="コネクタ: カギ線 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F145375-EB6A-4F9C-AC4E-145912C96476}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="2"/>
+          <a:endCxn id="42" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="4838701" y="2572481"/>
+          <a:ext cx="1468317" cy="706315"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>439617</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>137745</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="四角形: 角を丸くする 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0885CFAD-C53B-4BE3-A4F6-110B42ABAF8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5926017" y="3471495"/>
+          <a:ext cx="1027233" cy="376605"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>パーク選択</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>179511</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>172918</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>149835</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="直線矢印コネクタ 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E71F5C1-6650-4770-9A94-00E77BA430E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="53" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5665911" y="1993288"/>
+          <a:ext cx="3422407" cy="1490297"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>115768</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>90120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="四角形: 角を丸くする 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7A952B7-A66F-4EEA-81A2-5D52D5DAC131}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9031168" y="1518870"/>
+          <a:ext cx="1284407" cy="367080"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ゲームオーバー</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>172918</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>204420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="四角形: 角を丸くする 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11BA02E1-BB69-4C9C-9FD4-0DFE8050C251}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9088318" y="3300045"/>
+          <a:ext cx="1284407" cy="367080"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ゲームクリア</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>72171</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>306266</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>106973</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="コネクタ: カギ線 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1F81E21-3878-4ED8-8158-D9842553861A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="52" idx="2"/>
+          <a:endCxn id="63" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="9713120" y="1846201"/>
+          <a:ext cx="840398" cy="919895"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>306267</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>156795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="四角形: 角を丸くする 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F9FAA91-4074-4FEB-94BE-F78EF43B913A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10593267" y="2538045"/>
+          <a:ext cx="1027233" cy="376605"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リザルト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>129323</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>382469</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>211748</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="コネクタ: カギ線 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B1D5034-29BB-456B-B831-DA592FEA9714}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="53" idx="2"/>
+          <a:endCxn id="67" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="9903621" y="3494026"/>
+          <a:ext cx="592749" cy="938946"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent3">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>382468</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>23446</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="四角形: 角を丸くする 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11780673-E89A-42F0-89AA-3A16CDE6E081}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10669468" y="4071571"/>
+          <a:ext cx="1027233" cy="376605"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リザルト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>580650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>172950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AEC0649-3DA4-5515-7523-2BE098B35177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="704850" y="742950"/>
+          <a:ext cx="6048000" cy="3240000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F3B21A-00A8-CCB2-0D0E-27040BB038DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="1876425"/>
+          <a:ext cx="1371600" cy="1409700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>画像</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180978</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>57156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381002</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95256</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="二等辺三角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86DD4D83-BAAB-4500-9105-2244451C8174}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="6315077" y="2238382"/>
+          <a:ext cx="276225" cy="200024"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D8F5C87-0A2D-4D9C-9261-3BAD1D10579F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4143375" y="1238249"/>
+          <a:ext cx="1819276" cy="2200275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステータス表示</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39325516-1425-446D-B17B-108CB1B8D28F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4933950" y="3657600"/>
+          <a:ext cx="1762125" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>★</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>START GAME</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152403</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>161928</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>352427</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>200028</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="二等辺三角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FE954BA-6761-41E8-8091-48955C538271}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="800102" y="2343154"/>
+          <a:ext cx="276225" cy="200024"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E81A48E-FB01-45A6-8433-E506706FE277}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1581150" y="1428750"/>
+          <a:ext cx="952500" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>キャラ名</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,6 +2592,337 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC21973A-F6E6-42EA-BF4C-39601FB8FFC2}">
+  <dimension ref="A3:U35"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="B27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="B30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF25C95-5A4E-418C-B7C2-F586F1CC3EB1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53000610-87A2-4583-AF68-299DADAEC97E}">
+  <dimension ref="A2:Q20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC31936-D11B-4E05-89BA-FFB3F2FEB428}">
+  <dimension ref="A2:K25"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="31.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A23" s="4"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BE873E-4203-4B83-9865-E032F1668550}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>

--- a/doc/仕様書.xlsx
+++ b/doc/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirit_ygjlq3s\Desktop\Development\Project\MyEngine\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD0B7A6-8CC4-4A19-8ECF-043850642B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0849BEE2-FE95-4659-BCE6-39430792E548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{007E28DE-F532-4133-89C6-A8AB1947F25D}"/>
+    <workbookView xWindow="-28920" yWindow="-9750" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{007E28DE-F532-4133-89C6-A8AB1947F25D}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -318,6 +318,64 @@
   </si>
   <si>
     <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクトを複数配置ではなく、１枚の画像として配置する。</t>
+    <rPh sb="7" eb="11">
+      <t>フクスウハイチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択されたIDの武器情報を取得してそれを初期の武器として扱う。</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ブキジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要なシステム</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDが変わることによってX座標を移動させるシステム</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イドウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -382,7 +440,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -393,12 +451,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1786,192 +1838,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F3B21A-00A8-CCB2-0D0E-27040BB038DB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1362075" y="1876425"/>
-          <a:ext cx="1371600" cy="1409700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent4">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent4"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>画像</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>180978</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>57156</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>381002</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>95256</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="二等辺三角形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86DD4D83-BAAB-4500-9105-2244451C8174}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="6315077" y="2238382"/>
-          <a:ext cx="276225" cy="200024"/>
-        </a:xfrm>
-        <a:prstGeom prst="triangle">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent4">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent4"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>476251</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D8F5C87-0A2D-4D9C-9261-3BAD1D10579F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4143375" y="1238249"/>
-          <a:ext cx="1819276" cy="2200275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent4">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent4"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>ステータス表示</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>15</xdr:row>
@@ -2040,23 +1906,163 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AB49EAD-20AD-4F2A-9E86-2361DAB1E029}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552575" y="1304925"/>
+          <a:ext cx="1524000" cy="2276475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>火の書</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（画像）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2CC8672-6B1C-41CF-9240-97677C743489}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4029076" y="971550"/>
+          <a:ext cx="1952624" cy="2514600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>情報、ステータス</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>性能、特性</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>152403</xdr:colOff>
+      <xdr:colOff>95251</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>161928</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>352427</xdr:colOff>
+      <xdr:colOff>352426</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>200028</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="二等辺三角形 7">
+        <xdr:cNvPr id="11" name="二等辺三角形 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FE954BA-6761-41E8-8091-48955C538271}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1300C66-05A0-A3B5-DFDB-619D0D1E403C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2064,8 +2070,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="800102" y="2343154"/>
-          <a:ext cx="276225" cy="200024"/>
+          <a:off x="771526" y="2247900"/>
+          <a:ext cx="276225" cy="257175"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst/>
@@ -2100,34 +2106,34 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>523876</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="正方形/長方形 8">
+        <xdr:cNvPr id="12" name="二等辺三角形 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E81A48E-FB01-45A6-8433-E506706FE277}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F7636A0-5A95-4C8F-997C-35E0A8820ECD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1581150" y="1428750"/>
-          <a:ext cx="952500" cy="257175"/>
+        <a:xfrm rot="5400000">
+          <a:off x="6429376" y="2247900"/>
+          <a:ext cx="276225" cy="257175"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="triangle">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
@@ -2151,12 +2157,8 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>キャラ名</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2714,7 +2716,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53000610-87A2-4583-AF68-299DADAEC97E}">
-  <dimension ref="A2:Q20"/>
+  <dimension ref="A2:Q33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.4">
@@ -2759,6 +2761,42 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
     </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2771,12 +2809,11 @@
   <dimension ref="A2:K25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="31.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="4"/>
+      <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
@@ -2898,7 +2935,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A23" s="4"/>
+      <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2911,7 +2948,7 @@
       <c r="K23" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A25" s="5" t="s">
+      <c r="A25" t="s">
         <v>38</v>
       </c>
     </row>
